--- a/predictions_today.xlsx
+++ b/predictions_today.xlsx
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5625134843297392</v>
+        <v>0.5571080538797086</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.5221932527544487</v>
+        <v>0.5142162514885161</v>
       </c>
     </row>
     <row r="4">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4006968135980531</v>
+        <v>0.3859655755431511</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5929457689587833</v>
+        <v>0.5896214654879782</v>
       </c>
     </row>
     <row r="6">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4325176566446577</v>
+        <v>0.4177108850190657</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6913094527669575</v>
+        <v>0.689938905445056</v>
       </c>
     </row>
   </sheetData>
@@ -648,25 +648,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.8088235150477473</v>
+        <v>0.4599170293035004</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
     </row>
@@ -678,25 +678,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6864403770772514</v>
+        <v>0.4827781555170426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
     </row>
@@ -708,25 +708,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4122125376165192</v>
+        <v>0.3005047606899318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
     </row>
@@ -738,25 +738,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4045600917760909</v>
+        <v>0.6279263018770599</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
     </row>
@@ -768,25 +768,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5380263281477249</v>
+        <v>0.8107717682630592</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Miami Heat</t>
         </is>
       </c>
     </row>
@@ -798,25 +798,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6376593512634099</v>
+        <v>0.4006862551661797</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
     </row>
@@ -828,25 +828,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3045234596666993</v>
+        <v>0.3988692169407916</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
     </row>
@@ -858,25 +858,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.4907812256873122</v>
+        <v>0.6955566865182683</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
     </row>
@@ -888,25 +888,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.4620023769593694</v>
+        <v>0.6806913516062066</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
     </row>
@@ -918,25 +918,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6812716793689665</v>
+        <v>0.533890137211791</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8952581829657023</v>
+        <v>0.8982030146478444</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
